--- a/tables/table-3-baseline-model-results.xlsx
+++ b/tables/table-3-baseline-model-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E4FD764-6F2E-4073-8E15-E7B2356EF5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{3E4FD764-6F2E-4073-8E15-E7B2356EF5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68924438-ACF3-4A86-AED1-F0425B61ABB0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E0120D6-E0F4-4A0E-BE96-999DA8FCAB55}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Model</t>
   </si>
@@ -40,15 +40,6 @@
   </si>
   <si>
     <t>Test Accuracy (%)</t>
-  </si>
-  <si>
-    <t>Precision (Macro)</t>
-  </si>
-  <si>
-    <t>Recall (Macro)</t>
-  </si>
-  <si>
-    <t>F1-Score (Macro)</t>
   </si>
   <si>
     <t>VGG16</t>
@@ -106,20 +97,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <b/>
@@ -135,15 +122,21 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -162,83 +155,11 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -247,52 +168,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -608,267 +502,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89C7855C-5A04-412E-AB0C-64E10BA97935}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="4" width="12.42578125" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="7.42578125" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-    </row>
-    <row r="2" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="C3" s="5">
         <v>91.16</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>89.2</v>
       </c>
       <c r="E3" s="5">
         <v>92.8</v>
       </c>
-      <c r="F3" s="7">
-        <v>0.95</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0.93</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>11</v>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="C4" s="5">
         <v>94.21</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>92</v>
       </c>
       <c r="E4" s="5">
         <v>94.4</v>
       </c>
-      <c r="F4" s="7">
-        <v>0.96</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0.94</v>
-      </c>
-      <c r="H4" s="8">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C5" s="5">
         <v>96.49</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>96.4</v>
       </c>
       <c r="E5" s="5">
         <v>96.4</v>
       </c>
-      <c r="F5" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0.96</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
+    </row>
+    <row r="6" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C6" s="5">
         <v>98.2</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>93.6</v>
       </c>
       <c r="E6" s="5">
         <v>97.2</v>
       </c>
-      <c r="F6" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>17</v>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C7" s="5">
         <v>97.58</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>96</v>
       </c>
       <c r="E7" s="5">
         <v>98.4</v>
       </c>
-      <c r="F7" s="7">
-        <v>0.99</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.98</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>19</v>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="C8" s="5">
         <v>98.59</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>96</v>
       </c>
       <c r="E8" s="5">
         <v>98.8</v>
       </c>
-      <c r="F8" s="7">
-        <v>0.99</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0.99</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C9" s="5">
         <v>97.16</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>95.2</v>
       </c>
       <c r="E9" s="5">
         <v>97.2</v>
       </c>
-      <c r="F9" s="7">
-        <v>0.98</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="10">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="6">
         <v>97.34</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="6">
         <v>96.8</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="6">
         <v>97.6</v>
-      </c>
-      <c r="F10" s="12">
-        <v>0.98</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.98</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0.97</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
